--- a/Test upload format/Mudra/IA/2026 - 2027- SHG/CP1 26-27 SHG.xlsx
+++ b/Test upload format/Mudra/IA/2026 - 2027- SHG/CP1 26-27 SHG.xlsx
@@ -368,7 +368,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -383,109 +383,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -738,7 +732,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -762,16 +756,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -780,94 +774,92 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -886,27 +878,16 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1227,114 +1208,113 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:T25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.8571428571429" style="6" customWidth="1"/>
-    <col min="2" max="2" width="24.5714285714286" style="6" customWidth="1"/>
-    <col min="3" max="3" width="15.2857142857143" style="6" customWidth="1"/>
-    <col min="4" max="4" width="11.5714285714286" style="6" customWidth="1"/>
-    <col min="5" max="5" width="15" style="6" customWidth="1"/>
-    <col min="6" max="6" width="20.5714285714286" style="6" customWidth="1"/>
-    <col min="7" max="7" width="19" style="6" customWidth="1"/>
-    <col min="8" max="8" width="10.8571428571429" style="6" customWidth="1"/>
-    <col min="9" max="9" width="13.5714285714286" style="6" customWidth="1"/>
-    <col min="10" max="10" width="9" style="6"/>
-    <col min="11" max="11" width="17" style="6" customWidth="1"/>
-    <col min="12" max="12" width="15.8571428571429" style="6" customWidth="1"/>
-    <col min="13" max="13" width="18.5714285714286" style="6" customWidth="1"/>
-    <col min="14" max="14" width="17.2857142857143" style="6" customWidth="1"/>
-    <col min="15" max="15" width="13.2857142857143" style="6" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="6"/>
+    <col min="1" max="1" width="17.8571428571429" style="2" customWidth="1"/>
+    <col min="2" max="2" width="24.5714285714286" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.2857142857143" style="2" customWidth="1"/>
+    <col min="4" max="5" width="15" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.5714285714286" style="2" customWidth="1"/>
+    <col min="7" max="7" width="19" style="2" customWidth="1"/>
+    <col min="8" max="8" width="10.8571428571429" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.5714285714286" style="2" customWidth="1"/>
+    <col min="10" max="10" width="9" style="2"/>
+    <col min="11" max="11" width="17" style="2" customWidth="1"/>
+    <col min="12" max="12" width="15.8571428571429" style="2" customWidth="1"/>
+    <col min="13" max="13" width="18.5714285714286" style="2" customWidth="1"/>
+    <col min="14" max="14" width="17.2857142857143" style="2" customWidth="1"/>
+    <col min="15" max="15" width="13.2857142857143" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="P1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="Q1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="R1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:20">
-      <c r="A2" s="12" t="s">
+    <row r="2" s="1" customFormat="1" hidden="1" spans="1:20">
+      <c r="A2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12" t="s">
+      <c r="D2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>24</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="10" t="s">
         <v>26</v>
       </c>
       <c r="J2" s="1">
@@ -1346,46 +1326,46 @@
       <c r="L2" s="1">
         <v>1</v>
       </c>
-      <c r="M2" s="14">
+      <c r="M2" s="12">
         <v>2000000</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="N2" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
-      <c r="S2" s="12" t="s">
+      <c r="S2" s="10" t="s">
         <v>27</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:20">
-      <c r="A3" s="12" t="s">
+    <row r="3" s="1" customFormat="1" hidden="1" spans="1:20">
+      <c r="A3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="12" t="s">
+      <c r="D3" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="10" t="s">
         <v>24</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="10" t="s">
         <v>26</v>
       </c>
       <c r="J3" s="1">
@@ -1397,42 +1377,42 @@
       <c r="L3" s="1">
         <v>1</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="12">
         <v>2000000</v>
       </c>
-      <c r="N3" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="S3" s="12" t="s">
+      <c r="N3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="S3" s="10" t="s">
         <v>27</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:20">
-      <c r="A4" s="12" t="s">
+    <row r="4" s="1" customFormat="1" hidden="1" spans="1:20">
+      <c r="A4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="12" t="s">
+      <c r="D4" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="10" t="s">
         <v>24</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="10" t="s">
         <v>26</v>
       </c>
       <c r="J4" s="1">
@@ -1444,42 +1424,42 @@
       <c r="L4" s="1">
         <v>1</v>
       </c>
-      <c r="M4" s="14">
+      <c r="M4" s="12">
         <v>2000000</v>
       </c>
-      <c r="N4" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="S4" s="12" t="s">
+      <c r="N4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="S4" s="10" t="s">
         <v>27</v>
       </c>
       <c r="T4" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:20">
-      <c r="A5" s="12" t="s">
+    <row r="5" s="1" customFormat="1" hidden="1" spans="1:20">
+      <c r="A5" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="12" t="s">
+      <c r="D5" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="10" t="s">
         <v>24</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="10" t="s">
         <v>26</v>
       </c>
       <c r="J5" s="1">
@@ -1491,42 +1471,42 @@
       <c r="L5" s="1">
         <v>1</v>
       </c>
-      <c r="M5" s="14">
+      <c r="M5" s="12">
         <v>2000000</v>
       </c>
-      <c r="N5" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="S5" s="12" t="s">
+      <c r="N5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="S5" s="10" t="s">
         <v>27</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:20">
-      <c r="A6" s="12" t="s">
+    <row r="6" s="1" customFormat="1" hidden="1" spans="1:20">
+      <c r="A6" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="12" t="s">
+      <c r="D6" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="10" t="s">
         <v>24</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="10" t="s">
         <v>26</v>
       </c>
       <c r="J6" s="1">
@@ -1538,42 +1518,42 @@
       <c r="L6" s="1">
         <v>1</v>
       </c>
-      <c r="M6" s="14">
+      <c r="M6" s="12">
         <v>2000000</v>
       </c>
-      <c r="N6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="S6" s="12" t="s">
+      <c r="N6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="S6" s="10" t="s">
         <v>27</v>
       </c>
       <c r="T6" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:20">
-      <c r="A7" s="12" t="s">
+    <row r="7" s="1" customFormat="1" hidden="1" spans="1:20">
+      <c r="A7" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="12" t="s">
+      <c r="D7" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="10" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="10" t="s">
         <v>26</v>
       </c>
       <c r="J7" s="1">
@@ -1585,42 +1565,42 @@
       <c r="L7" s="1">
         <v>1</v>
       </c>
-      <c r="M7" s="14">
+      <c r="M7" s="12">
         <v>2000000</v>
       </c>
-      <c r="N7" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="S7" s="12" t="s">
+      <c r="N7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="S7" s="10" t="s">
         <v>27</v>
       </c>
       <c r="T7" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:20">
-      <c r="A8" s="12" t="s">
+    <row r="8" s="1" customFormat="1" hidden="1" spans="1:20">
+      <c r="A8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="12" t="s">
+      <c r="D8" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="10" t="s">
         <v>24</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="10" t="s">
         <v>26</v>
       </c>
       <c r="J8" s="1">
@@ -1632,42 +1612,42 @@
       <c r="L8" s="1">
         <v>1</v>
       </c>
-      <c r="M8" s="14">
+      <c r="M8" s="12">
         <v>2000000</v>
       </c>
-      <c r="N8" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="S8" s="12" t="s">
+      <c r="N8" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="S8" s="10" t="s">
         <v>27</v>
       </c>
       <c r="T8" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:20">
-      <c r="A9" s="12" t="s">
+    <row r="9" s="1" customFormat="1" hidden="1" spans="1:20">
+      <c r="A9" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="12" t="s">
+      <c r="D9" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="10" t="s">
         <v>24</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="10" t="s">
         <v>26</v>
       </c>
       <c r="J9" s="1">
@@ -1679,42 +1659,42 @@
       <c r="L9" s="1">
         <v>1</v>
       </c>
-      <c r="M9" s="14">
+      <c r="M9" s="12">
         <v>2000000</v>
       </c>
-      <c r="N9" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="S9" s="12" t="s">
+      <c r="N9" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="S9" s="10" t="s">
         <v>27</v>
       </c>
       <c r="T9" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="1:20">
-      <c r="A10" s="12" t="s">
+    <row r="10" s="1" customFormat="1" hidden="1" spans="1:20">
+      <c r="A10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="12" t="s">
+      <c r="D10" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="10" t="s">
         <v>24</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="10" t="s">
         <v>26</v>
       </c>
       <c r="J10" s="1">
@@ -1726,42 +1706,42 @@
       <c r="L10" s="1">
         <v>1</v>
       </c>
-      <c r="M10" s="14">
+      <c r="M10" s="12">
         <v>2000000</v>
       </c>
-      <c r="N10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="S10" s="12" t="s">
+      <c r="N10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="S10" s="10" t="s">
         <v>27</v>
       </c>
       <c r="T10" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" spans="1:20">
-      <c r="A11" s="12" t="s">
+    <row r="11" s="1" customFormat="1" hidden="1" spans="1:20">
+      <c r="A11" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="12" t="s">
+      <c r="D11" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="10" t="s">
         <v>24</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="10" t="s">
         <v>26</v>
       </c>
       <c r="J11" s="1">
@@ -1773,611 +1753,616 @@
       <c r="L11" s="1">
         <v>1</v>
       </c>
-      <c r="M11" s="14">
+      <c r="M11" s="12">
         <v>2000000</v>
       </c>
-      <c r="N11" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="S11" s="12" t="s">
+      <c r="N11" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="S11" s="10" t="s">
         <v>27</v>
       </c>
       <c r="T11" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:20">
-      <c r="A12" s="15" t="s">
+    <row r="12" s="1" customFormat="1" hidden="1" spans="1:20">
+      <c r="A12" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="15" t="s">
+      <c r="D12" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="15" t="s">
+      <c r="G12" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="2">
-        <v>1</v>
-      </c>
-      <c r="K12" s="2">
-        <v>1</v>
-      </c>
-      <c r="L12" s="2">
-        <v>1</v>
-      </c>
-      <c r="M12" s="17">
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
+      <c r="M12" s="12">
         <v>2000000</v>
       </c>
-      <c r="N12" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="S12" s="15" t="s">
+      <c r="N12" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="S12" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="T12" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" spans="1:20">
-      <c r="A13" s="15" t="s">
+      <c r="T12" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" hidden="1" spans="1:20">
+      <c r="A13" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15" t="s">
+      <c r="D13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="15" t="s">
+      <c r="G13" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="J13" s="2">
-        <v>1</v>
-      </c>
-      <c r="K13" s="2">
-        <v>1</v>
-      </c>
-      <c r="L13" s="2">
-        <v>1</v>
-      </c>
-      <c r="M13" s="17">
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
+      <c r="M13" s="12">
         <v>2000000</v>
       </c>
-      <c r="N13" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="S13" s="15" t="s">
+      <c r="N13" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="S13" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="T13" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" s="3" customFormat="1" spans="1:20">
-      <c r="A14" s="18" t="s">
+      <c r="T13" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" hidden="1" spans="1:20">
+      <c r="A14" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="18" t="s">
+      <c r="D14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K14" s="20">
-        <v>1</v>
-      </c>
-      <c r="L14" s="20">
-        <v>1</v>
-      </c>
-      <c r="M14" s="21">
+      <c r="G14" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="2">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2">
+        <v>1</v>
+      </c>
+      <c r="M14" s="14">
         <v>1000000</v>
       </c>
-      <c r="N14" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="S14" s="19" t="s">
+      <c r="N14" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="S14" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="T14" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" s="3" customFormat="1" spans="1:20">
-      <c r="A15" s="18" t="s">
+      <c r="T14" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" hidden="1" spans="1:20">
+      <c r="A15" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="18" t="s">
+      <c r="D15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K15" s="20">
-        <v>1</v>
-      </c>
-      <c r="L15" s="20">
-        <v>1</v>
-      </c>
-      <c r="M15" s="21">
+      <c r="G15" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="2">
+        <v>1</v>
+      </c>
+      <c r="L15" s="2">
+        <v>1</v>
+      </c>
+      <c r="M15" s="14">
         <v>2000000</v>
       </c>
-      <c r="N15" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="S15" s="19" t="s">
+      <c r="N15" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="S15" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="T15" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" s="3" customFormat="1" spans="1:20">
-      <c r="A16" s="18" t="s">
+      <c r="T15" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" hidden="1" spans="1:20">
+      <c r="A16" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="19" t="s">
+      <c r="D16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G16" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K16" s="20">
-        <v>1</v>
-      </c>
-      <c r="L16" s="20">
-        <v>1</v>
-      </c>
-      <c r="M16" s="22">
+      <c r="G16" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2">
+        <v>1</v>
+      </c>
+      <c r="M16" s="14">
         <v>1000000</v>
       </c>
-      <c r="N16" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="S16" s="19" t="s">
+      <c r="N16" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="S16" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="T16" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" s="3" customFormat="1" spans="1:20">
-      <c r="A17" s="18" t="s">
+      <c r="T16" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" hidden="1" spans="1:20">
+      <c r="A17" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" s="18" t="s">
+      <c r="D17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G17" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K17" s="20">
-        <v>1</v>
-      </c>
-      <c r="L17" s="20">
-        <v>1</v>
-      </c>
-      <c r="M17" s="22">
+      <c r="G17" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" s="2">
+        <v>1</v>
+      </c>
+      <c r="L17" s="2">
+        <v>1</v>
+      </c>
+      <c r="M17" s="14">
         <v>2000000</v>
       </c>
-      <c r="N17" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="S17" s="19" t="s">
+      <c r="N17" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="S17" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="T17" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" s="3" customFormat="1" spans="1:20">
-      <c r="A18" s="18" t="s">
+      <c r="T17" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" hidden="1" spans="1:20">
+      <c r="A18" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18" s="18" t="s">
+      <c r="D18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="G18" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K18" s="20">
-        <v>1</v>
-      </c>
-      <c r="L18" s="20">
-        <v>1</v>
-      </c>
-      <c r="M18" s="21">
+      <c r="G18" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2">
+        <v>1</v>
+      </c>
+      <c r="M18" s="14">
         <v>1000000</v>
       </c>
-      <c r="N18" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="S18" s="19" t="s">
+      <c r="N18" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="S18" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="T18" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" s="4" customFormat="1" spans="1:20">
-      <c r="A19" s="23" t="s">
+      <c r="T18" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" s="3" customFormat="1" ht="14" hidden="1" customHeight="1" spans="1:20">
+      <c r="A19" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="23" t="s">
+      <c r="D19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="23" t="s">
+      <c r="F19" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="G19" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K19" s="4">
-        <v>1</v>
-      </c>
-      <c r="L19" s="4">
-        <v>1</v>
-      </c>
-      <c r="M19" s="24">
+      <c r="G19" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" s="3">
+        <v>1</v>
+      </c>
+      <c r="L19" s="3">
+        <v>1</v>
+      </c>
+      <c r="M19" s="16">
         <v>2000000</v>
       </c>
-      <c r="N19" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="S19" s="23" t="s">
+      <c r="N19" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="S19" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="T19" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" s="5" customFormat="1" spans="1:20">
-      <c r="A20" s="25" t="s">
+      <c r="T19" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" s="4" customFormat="1" spans="1:20">
+      <c r="A20" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C20" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F20" s="25" t="s">
+      <c r="F20" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="K20" s="5">
-        <v>1</v>
-      </c>
-      <c r="L20" s="5">
-        <v>1</v>
-      </c>
-      <c r="M20" s="27">
+      <c r="G20" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20" s="4">
+        <v>1</v>
+      </c>
+      <c r="L20" s="4">
+        <v>1</v>
+      </c>
+      <c r="M20" s="18">
         <v>1000000</v>
       </c>
-      <c r="N20" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="S20" s="25" t="s">
+      <c r="N20" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="S20" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="T20" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" s="5" customFormat="1" spans="1:20">
-      <c r="A21" s="25" t="s">
+      <c r="T20" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" s="4" customFormat="1" spans="1:20">
+      <c r="A21" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F21" s="25" t="s">
+      <c r="F21" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="G21" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="H21" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="K21" s="5">
-        <v>1</v>
-      </c>
-      <c r="L21" s="5">
-        <v>1</v>
-      </c>
-      <c r="M21" s="27">
+      <c r="G21" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" s="4">
+        <v>1</v>
+      </c>
+      <c r="L21" s="4">
+        <v>1</v>
+      </c>
+      <c r="M21" s="18">
         <v>2000000</v>
       </c>
-      <c r="N21" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="S21" s="25" t="s">
+      <c r="N21" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="S21" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="T21" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" s="5" customFormat="1" spans="1:20">
-      <c r="A22" s="25" t="s">
+      <c r="T21" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" s="4" customFormat="1" spans="1:20">
+      <c r="A22" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C22" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F22" s="25" t="s">
+      <c r="F22" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G22" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="K22" s="5">
-        <v>1</v>
-      </c>
-      <c r="L22" s="5">
-        <v>1</v>
-      </c>
-      <c r="M22" s="27">
+      <c r="G22" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" s="4">
+        <v>1</v>
+      </c>
+      <c r="L22" s="4">
+        <v>1</v>
+      </c>
+      <c r="M22" s="18">
         <v>1000000</v>
       </c>
-      <c r="N22" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="S22" s="25" t="s">
+      <c r="N22" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="S22" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="T22" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" s="5" customFormat="1" spans="1:20">
-      <c r="A23" s="25" t="s">
+      <c r="T22" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" s="4" customFormat="1" spans="1:20">
+      <c r="A23" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C23" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F23" s="25" t="s">
+      <c r="F23" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="G23" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="K23" s="5">
-        <v>1</v>
-      </c>
-      <c r="L23" s="5">
-        <v>1</v>
-      </c>
-      <c r="M23" s="27">
+      <c r="G23" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" s="4">
+        <v>1</v>
+      </c>
+      <c r="L23" s="4">
+        <v>1</v>
+      </c>
+      <c r="M23" s="18">
         <v>2000000</v>
       </c>
-      <c r="N23" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="S23" s="25" t="s">
+      <c r="N23" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="S23" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="T23" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" s="5" customFormat="1" spans="1:20">
-      <c r="A24" s="25" t="s">
+      <c r="T23" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" s="4" customFormat="1" spans="1:20">
+      <c r="A24" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="25" t="s">
+      <c r="B24" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C24" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F24" s="25" t="s">
+      <c r="F24" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="G24" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="H24" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="K24" s="5">
-        <v>1</v>
-      </c>
-      <c r="L24" s="5">
-        <v>1</v>
-      </c>
-      <c r="M24" s="27">
+      <c r="G24" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K24" s="4">
+        <v>1</v>
+      </c>
+      <c r="L24" s="4">
+        <v>1</v>
+      </c>
+      <c r="M24" s="18">
         <v>1000000</v>
       </c>
-      <c r="N24" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="S24" s="25" t="s">
+      <c r="N24" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="S24" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="T24" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" s="5" customFormat="1" spans="1:20">
-      <c r="A25" s="25" t="s">
+      <c r="T24" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" s="4" customFormat="1" spans="1:20">
+      <c r="A25" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="25" t="s">
+      <c r="B25" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C25" s="25" t="s">
+      <c r="C25" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F25" s="25" t="s">
+      <c r="F25" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G25" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="H25" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="K25" s="5">
-        <v>1</v>
-      </c>
-      <c r="L25" s="5">
-        <v>1</v>
-      </c>
-      <c r="M25" s="27">
+      <c r="G25" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K25" s="4">
+        <v>1</v>
+      </c>
+      <c r="L25" s="4">
+        <v>1</v>
+      </c>
+      <c r="M25" s="18">
         <v>2000000</v>
       </c>
-      <c r="N25" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="S25" s="25" t="s">
+      <c r="N25" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="S25" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="T25" s="5" t="s">
+      <c r="T25" s="4" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:T25" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="IA"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
